--- a/docs/data/beidan_26089_dashboard.xlsx
+++ b/docs/data/beidan_26089_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26089期 比赛看板（皇冠历史相同亚盘） — 2026-08-28</t>
+          <t>⚽ 北京单场26089期 比赛看板（皇冠历史相同亚盘） — 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -980,10 +1004,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1036,10 +1064,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>3:5</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1092,10 +1124,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1204,10 +1244,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>受球半</t>
@@ -1260,10 +1304,14 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1316,10 +1364,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1372,10 +1424,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -1428,10 +1484,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1484,10 +1544,14 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1540,10 +1604,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1596,10 +1664,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1652,10 +1724,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1708,10 +1784,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1764,10 +1844,14 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1820,10 +1904,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1876,10 +1964,14 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1932,10 +2024,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1988,10 +2084,14 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -2044,10 +2144,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2100,10 +2204,14 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2156,10 +2264,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2212,10 +2324,14 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2268,10 +2384,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2324,10 +2444,14 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2380,10 +2504,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+          <t>6:1</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2436,10 +2564,14 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2492,10 +2624,14 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2548,10 +2684,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2604,10 +2744,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2660,10 +2804,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -2716,10 +2864,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2772,10 +2924,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2828,10 +2984,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2884,10 +3044,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2940,10 +3104,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -2996,10 +3164,14 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -3052,10 +3224,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -3108,10 +3284,14 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3164,10 +3344,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -3220,10 +3404,14 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3276,10 +3464,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -3332,10 +3524,14 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3388,10 +3584,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+          <t>5:4</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -3444,10 +3644,14 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3500,10 +3704,14 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -3556,10 +3764,14 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3612,10 +3824,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3668,10 +3884,14 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3724,10 +3944,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>受球半</t>
@@ -3780,10 +4004,14 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3836,10 +4064,14 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3892,10 +4124,14 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3948,10 +4184,14 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4004,10 +4244,14 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4060,10 +4304,14 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -4116,10 +4364,14 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -4172,10 +4424,14 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4208,7 +4464,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>08-29 09:00</t>
+          <t>08-29 10:00</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -4228,10 +4484,14 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4284,10 +4544,14 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4544,7 +4808,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>08-29 17:00</t>
+          <t>08-29 17:30</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -6840,7 +7104,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>08-29 20:00</t>
+          <t>08-30 23:00</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -9192,7 +9456,7 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>08-29 22:00</t>
+          <t>08-30 23:00</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
@@ -10108,20 +10372,24 @@
         </is>
       </c>
       <c r="H173" s="5" t="inlineStr"/>
-      <c r="I173" s="5" t="inlineStr"/>
-      <c r="J173" s="6" t="inlineStr">
-        <is>
-          <t>38%</t>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>一球/球半</t>
+        </is>
+      </c>
+      <c r="J173" s="8" t="inlineStr">
+        <is>
+          <t>59%</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
         <is>
-          <t>26%</t>
-        </is>
-      </c>
-      <c r="L173" s="6" t="inlineStr">
-        <is>
-          <t>35%</t>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="L173" s="5" t="inlineStr">
+        <is>
+          <t>18%</t>
         </is>
       </c>
     </row>
@@ -10160,20 +10428,24 @@
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr"/>
-      <c r="I174" s="4" t="inlineStr"/>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>37%</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10908,7 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>08-30 00:00</t>
+          <t>08-30 23:00</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
@@ -11756,7 +12028,7 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>08-29 23:00</t>
+          <t>08-30 02:00</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
@@ -16008,7 +16280,7 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>08-29 23:00</t>
+          <t>08-30 21:00</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
@@ -17292,7 +17564,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>08-29 23:00</t>
+          <t>08-30 23:00</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -17344,7 +17616,7 @@
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>08-29 23:00</t>
+          <t>08-30 23:00</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
@@ -17620,7 +17892,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>08-29 02:45</t>
+          <t>08-30 23:00</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -18572,7 +18844,7 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>08-29 23:00</t>
+          <t>08-31 00:30</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
@@ -19244,7 +19516,7 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>08-29 23:00</t>
+          <t>08-31 01:15</t>
         </is>
       </c>
       <c r="D337" s="5" t="inlineStr">
@@ -19632,7 +19904,7 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>08-29 23:00</t>
+          <t>08-31 02:00</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">

--- a/docs/data/beidan_26089_dashboard.xlsx
+++ b/docs/data/beidan_26089_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26089期 比赛看板（皇冠历史相同亚盘） — 2026-08-29</t>
+          <t>⚽ 北京单场26089期 比赛看板（皇冠历史相同亚盘） — 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4604,10 +4604,14 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4660,10 +4664,14 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -4716,10 +4724,14 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4772,10 +4784,14 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4828,10 +4844,14 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -4884,10 +4904,14 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -4940,10 +4964,14 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4996,10 +5024,14 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5052,10 +5084,14 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5108,10 +5144,14 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -5164,10 +5204,14 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -5220,10 +5264,14 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5276,10 +5324,14 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5332,10 +5384,14 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5388,10 +5444,14 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5444,10 +5504,14 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5500,10 +5564,14 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5556,10 +5624,14 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5612,10 +5684,14 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5668,10 +5744,14 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5724,10 +5804,14 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5780,10 +5864,14 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -5836,10 +5924,14 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5892,10 +5984,14 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5948,10 +6044,14 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6004,10 +6104,14 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6060,10 +6164,14 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6116,10 +6224,14 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6172,10 +6284,14 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
+          <t>5:3</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6228,10 +6344,14 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr"/>
+          <t>2:5</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -6284,10 +6404,14 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
+          <t>3:4</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6340,10 +6464,14 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6396,10 +6524,14 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6452,10 +6584,14 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6508,10 +6644,14 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -6564,10 +6704,14 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6620,10 +6764,14 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -6676,10 +6824,14 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -6732,10 +6884,14 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -6788,10 +6944,14 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6844,10 +7004,14 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -6900,10 +7064,14 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6956,10 +7124,14 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7012,10 +7184,14 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7068,10 +7244,14 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7124,10 +7304,14 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>＊</t>
+        </is>
+      </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7180,10 +7364,14 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -7236,10 +7424,14 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7292,10 +7484,14 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -7348,10 +7544,14 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -7404,10 +7604,14 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -7460,10 +7664,14 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7516,10 +7724,14 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -7572,10 +7784,14 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -7628,10 +7844,14 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -7684,10 +7904,14 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -7740,10 +7964,14 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7796,10 +8024,14 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7852,10 +8084,14 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -7908,10 +8144,14 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -7964,10 +8204,14 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8020,10 +8264,14 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8076,10 +8324,14 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8132,10 +8384,14 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8188,10 +8444,14 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8244,10 +8504,14 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8300,10 +8564,14 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8356,10 +8624,14 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8412,10 +8684,14 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -8468,10 +8744,14 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8524,10 +8804,14 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8580,10 +8864,14 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8636,10 +8924,14 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8692,10 +8984,14 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8748,10 +9044,14 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8804,10 +9104,14 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8860,10 +9164,14 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -8916,10 +9224,14 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -8972,10 +9284,14 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9028,10 +9344,14 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9084,10 +9404,14 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9140,10 +9464,14 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -9196,10 +9524,14 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9252,10 +9584,14 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -9308,10 +9644,14 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
           <t>两球</t>
@@ -9364,10 +9704,14 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -9420,10 +9764,14 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9476,10 +9824,14 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>＊</t>
+        </is>
+      </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9532,10 +9884,14 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9588,10 +9944,14 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -9644,10 +10004,14 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -9700,10 +10064,14 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -9756,10 +10124,14 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9812,10 +10184,14 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -9868,10 +10244,14 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9924,10 +10304,14 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -9980,10 +10364,14 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10036,10 +10424,14 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10092,10 +10484,14 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10148,10 +10544,14 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr"/>
+          <t>5:2</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10204,10 +10604,14 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10260,10 +10664,14 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -12052,20 +12460,24 @@
         </is>
       </c>
       <c r="H203" s="5" t="inlineStr"/>
-      <c r="I203" s="5" t="inlineStr"/>
+      <c r="I203" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="K203" s="5" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -13256,7 +13668,7 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>08-30 04:30</t>
+          <t>08-30 04:40</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
@@ -13648,7 +14060,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>08-30 07:30</t>
+          <t>08-30 07:40</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -13704,7 +14116,7 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>08-30 07:30</t>
+          <t>08-30 07:40</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
@@ -13760,7 +14172,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>08-30 07:30</t>
+          <t>08-30 07:40</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -13816,7 +14228,7 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>08-30 07:30</t>
+          <t>08-30 07:40</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
@@ -13872,7 +14284,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>08-30 07:30</t>
+          <t>08-30 07:40</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -14096,7 +14508,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>08-30 08:30</t>
+          <t>08-30 08:40</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -14152,7 +14564,7 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>08-30 08:30</t>
+          <t>08-30 08:40</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
@@ -14208,7 +14620,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>08-30 08:30</t>
+          <t>08-30 08:40</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -14264,7 +14676,7 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>08-30 08:30</t>
+          <t>08-30 08:40</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
@@ -14376,7 +14788,7 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>08-30 09:30</t>
+          <t>08-30 09:40</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
@@ -14432,7 +14844,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>08-30 10:30</t>
+          <t>08-30 10:40</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -14488,7 +14900,7 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>08-30 10:30</t>
+          <t>08-30 10:40</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
@@ -16304,20 +16716,24 @@
         </is>
       </c>
       <c r="H279" s="5" t="inlineStr"/>
-      <c r="I279" s="5" t="inlineStr"/>
+      <c r="I279" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="K279" s="5" t="inlineStr">
-        <is>
-          <t>31%</t>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="K279" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
         </is>
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>12%</t>
         </is>
       </c>
     </row>
@@ -17588,20 +18004,24 @@
         </is>
       </c>
       <c r="H302" s="4" t="inlineStr"/>
-      <c r="I302" s="4" t="inlineStr"/>
+      <c r="I302" s="4" t="inlineStr">
+        <is>
+          <t>球半</t>
+        </is>
+      </c>
       <c r="J302" s="4" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="K302" s="4" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -17640,20 +18060,24 @@
         </is>
       </c>
       <c r="H303" s="5" t="inlineStr"/>
-      <c r="I303" s="5" t="inlineStr"/>
-      <c r="J303" s="6" t="inlineStr">
+      <c r="I303" s="5" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
+      <c r="J303" s="5" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L303" s="6" t="inlineStr">
         <is>
           <t>38%</t>
-        </is>
-      </c>
-      <c r="K303" s="5" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="L303" s="5" t="inlineStr">
-        <is>
-          <t>29%</t>
         </is>
       </c>
     </row>
@@ -19652,20 +20076,24 @@
         </is>
       </c>
       <c r="H339" s="5" t="inlineStr"/>
-      <c r="I339" s="5" t="inlineStr"/>
-      <c r="J339" s="6" t="inlineStr">
-        <is>
-          <t>39%</t>
+      <c r="I339" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
+      <c r="J339" s="8" t="inlineStr">
+        <is>
+          <t>48%</t>
         </is>
       </c>
       <c r="K339" s="5" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
@@ -19928,20 +20356,24 @@
         </is>
       </c>
       <c r="H344" s="4" t="inlineStr"/>
-      <c r="I344" s="4" t="inlineStr"/>
+      <c r="I344" s="4" t="inlineStr">
+        <is>
+          <t>平手</t>
+        </is>
+      </c>
       <c r="J344" s="4" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K344" s="4" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L344" s="4" t="inlineStr">
+        <is>
           <t>38%</t>
-        </is>
-      </c>
-      <c r="K344" s="4" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="L344" s="4" t="inlineStr">
-        <is>
-          <t>29%</t>
         </is>
       </c>
     </row>
